--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbashyam2\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\IP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2201A79-E387-49B4-B309-C36095AF7EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117FB1F9-5ABF-4923-BA16-4B29D400FD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4BD37116-B58A-4656-9812-8F2AAB833C8E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4BD37116-B58A-4656-9812-8F2AAB833C8E}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1834,7 +1834,7 @@
         <v>162</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>163</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117FB1F9-5ABF-4923-BA16-4B29D400FD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE48188-5173-4A05-987D-6CB1DD946312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4BD37116-B58A-4656-9812-8F2AAB833C8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4BD37116-B58A-4656-9812-8F2AAB833C8E}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="347">
   <si>
     <t>StepNo</t>
   </si>
@@ -1091,6 +1091,9 @@
   </si>
   <si>
     <t>Wait for element to load for despatch volume patient selection</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2327,7 @@
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2409,7 +2412,7 @@
         <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/CaseNote/LSTP_CaseNote_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\CaseNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE48188-5173-4A05-987D-6CB1DD946312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72243E99-0A48-42DF-AA60-60D63774F487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4BD37116-B58A-4656-9812-8F2AAB833C8E}"/>
   </bookViews>
@@ -4311,7 +4311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>127</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>256</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>287</v>
